--- a/survey_templates/034_ai_prompt_engineering_course_feedback--survey_templates.xlsx
+++ b/survey_templates/034_ai_prompt_engineering_course_feedback--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -946,8 +946,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -975,12 +975,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'1_-_poor',_'value':_1}</t>
+          <t>1_-_poor</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': '1 - Poor', 'value': 1}</t>
+          <t>1 - Poor</t>
         </is>
       </c>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'2_-_below_average',_'value':_2}</t>
+          <t>2_-_below_average</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': '2 - Below Average', 'value': 2}</t>
+          <t>2 - Below Average</t>
         </is>
       </c>
     </row>
@@ -1009,12 +1009,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'3_-_average',_'value':_3}</t>
+          <t>3_-_average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': '3 - Average', 'value': 3}</t>
+          <t>3 - Average</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'4_-_good',_'value':_4}</t>
+          <t>4_-_good</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '4 - Good', 'value': 4}</t>
+          <t>4 - Good</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1043,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'5_-_excellent',_'value':_5}</t>
+          <t>5_-_excellent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '5 - Excellent', 'value': 5}</t>
+          <t>5 - Excellent</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'zero-shot_/_one-shot_prompting',_'value':_'zero_shot'}</t>
+          <t>zero-shot_/_one-shot_prompting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Zero-shot / One-shot Prompting', 'value': 'zero_shot'}</t>
+          <t>Zero-shot / One-shot Prompting</t>
         </is>
       </c>
     </row>
@@ -1077,12 +1077,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'few-shot_learning',_'value':_'few_shot'}</t>
+          <t>few-shot_learning</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Few-shot Learning', 'value': 'few_shot'}</t>
+          <t>Few-shot Learning</t>
         </is>
       </c>
     </row>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'chain-of-thought_(cot)_prompting',_'value':_'cot'}</t>
+          <t>chain-of-thought_(cot)_prompting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Chain-of-Thought (CoT) Prompting', 'value': 'cot'}</t>
+          <t>Chain-of-Thought (CoT) Prompting</t>
         </is>
       </c>
     </row>
@@ -1111,12 +1111,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'iterative_refinement',_'value':_'refinement'}</t>
+          <t>iterative_refinement</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Iterative Refinement', 'value': 'refinement'}</t>
+          <t>Iterative Refinement</t>
         </is>
       </c>
     </row>
@@ -1128,12 +1128,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'role-based_prompting',_'value':_'role_based'}</t>
+          <t>role-based_prompting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Role-based Prompting', 'value': 'role_based'}</t>
+          <t>Role-based Prompting</t>
         </is>
       </c>
     </row>
@@ -1145,12 +1145,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'extremely_valuable',_'value':_'extremely_valuable'}</t>
+          <t>extremely_valuable</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely Valuable', 'value': 'extremely_valuable'}</t>
+          <t>Extremely Valuable</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_valuable',_'value':_'somewhat_valuable'}</t>
+          <t>somewhat_valuable</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Valuable', 'value': 'somewhat_valuable'}</t>
+          <t>Somewhat Valuable</t>
         </is>
       </c>
     </row>
@@ -1179,12 +1179,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral', 'value': 'neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1196,12 +1196,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_valuable',_'value':_'not_valuable'}</t>
+          <t>not_very_valuable</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Not very valuable', 'value': 'not_valuable'}</t>
+          <t>Not very valuable</t>
         </is>
       </c>
     </row>
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'too_fast',_'value':_'too_fast'}</t>
+          <t>too_fast</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Too Fast', 'value': 'too_fast'}</t>
+          <t>Too Fast</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'just_right',_'value':_'just_right'}</t>
+          <t>just_right</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Just Right', 'value': 'just_right'}</t>
+          <t>Just Right</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'too_slow',_'value':_'too_slow'}</t>
+          <t>too_slow</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Too Slow', 'value': 'too_slow'}</t>
+          <t>Too Slow</t>
         </is>
       </c>
     </row>
@@ -1264,12 +1264,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'maybe',_'value':_'maybe'}</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe', 'value': 'maybe'}</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
